--- a/registration_forms/039_yoga_studio_membership_form--registration_forms.xlsx
+++ b/registration_forms/039_yoga_studio_membership_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>form_ids_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Ids 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1158,7 +1158,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
